--- a/data/trans_dic/P1408-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1408-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,19 +684,19 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,47</t>
+          <t>1,88; 6,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,25</t>
+          <t>0,32; 3,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,63</t>
+          <t>0,96; 5,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,73</t>
+          <t>0,49; 2,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,19</t>
+          <t>0,36; 4,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,62</t>
+          <t>0,59; 2,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,55</t>
+          <t>0,99; 3,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,77</t>
+          <t>0,53; 2,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,1</t>
+          <t>0,7; 3,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,24</t>
+          <t>0,76; 2,3</t>
         </is>
       </c>
     </row>
@@ -804,47 +804,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>1,95%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,75</t>
+          <t>3,23; 7,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,45</t>
+          <t>2,02; 5,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,42</t>
+          <t>1,45; 4,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,5</t>
+          <t>1,02; 3,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,66</t>
+          <t>2,31; 5,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,44</t>
+          <t>0,41; 2,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,73</t>
+          <t>0,63; 2,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,46</t>
+          <t>1,06; 3,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,73</t>
+          <t>3,15; 5,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,33</t>
+          <t>1,4; 3,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,07</t>
+          <t>1,34; 3,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,86</t>
+          <t>1,21; 2,89</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,93</t>
+          <t>2,27; 7,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,67</t>
+          <t>0,96; 4,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,12</t>
+          <t>0,46; 2,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,49</t>
+          <t>1,88; 5,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,44</t>
+          <t>0,28; 2,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,32</t>
+          <t>0,6; 3,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,72</t>
+          <t>0,31; 2,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,79</t>
+          <t>2,03; 4,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,8</t>
+          <t>1,47; 3,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,23</t>
+          <t>1,07; 3,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,26</t>
+          <t>0,53; 2,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,34</t>
+          <t>2,26; 4,29</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,58</t>
+          <t>2,49; 6,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,84</t>
+          <t>1,39; 5,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,53</t>
+          <t>1,3; 4,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,04</t>
+          <t>2,14; 6,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,54</t>
+          <t>0,61; 3,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,62</t>
+          <t>1,27; 4,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,04</t>
+          <t>0,51; 3,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,23</t>
+          <t>2,02; 6,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,33</t>
+          <t>1,93; 4,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,36</t>
+          <t>1,69; 4,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,13</t>
+          <t>1,14; 3,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,05</t>
+          <t>2,36; 5,46</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 7,71</t>
+          <t>1,95; 7,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,07</t>
+          <t>0,48; 4,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,95</t>
+          <t>0,85; 4,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,22</t>
+          <t>0,76; 3,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,81</t>
+          <t>1,89; 8,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,99</t>
+          <t>0,7; 2,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,55</t>
+          <t>2,63; 6,54</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,48</t>
+          <t>0,25; 2,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,1</t>
+          <t>0,69; 2,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,91</t>
+          <t>1,0; 2,76</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,28</t>
+          <t>0,73; 4,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,13</t>
+          <t>2,33; 8,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,36</t>
+          <t>0,38; 3,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,94</t>
+          <t>2,82; 6,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,33</t>
+          <t>0,37; 3,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,87</t>
+          <t>0,34; 3,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,73</t>
+          <t>0,43; 3,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,64</t>
+          <t>2,32; 5,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,88</t>
+          <t>0,75; 3,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,71</t>
+          <t>1,62; 4,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,96</t>
+          <t>0,73; 3,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,67</t>
+          <t>3,12; 5,65</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,19</t>
+          <t>3,04; 6,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,15</t>
+          <t>0,46; 2,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,02</t>
+          <t>0,88; 3,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,25</t>
+          <t>1,58; 3,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,89</t>
+          <t>2,11; 5,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,15</t>
+          <t>0,47; 2,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,69</t>
+          <t>0,76; 2,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,18</t>
+          <t>2,14; 4,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,16</t>
+          <t>2,89; 5,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,72</t>
+          <t>0,63; 1,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,5</t>
+          <t>0,99; 2,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,55</t>
+          <t>2,24; 4,15</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,94</t>
+          <t>3,08; 5,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,95</t>
+          <t>0,73; 2,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,63</t>
+          <t>0,93; 2,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,51</t>
+          <t>1,23; 3,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,14</t>
+          <t>2,48; 5,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,48</t>
+          <t>0,25; 1,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,42</t>
+          <t>0,62; 2,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,18</t>
+          <t>1,41; 3,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,26</t>
+          <t>3,12; 5,12</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,84</t>
+          <t>0,68; 1,8</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,1</t>
+          <t>0,92; 2,05</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,58</t>
+          <t>1,53; 2,74</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,82</t>
+          <t>3,54; 4,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,73</t>
+          <t>1,61; 2,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,46</t>
+          <t>1,53; 2,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,94</t>
+          <t>2,05; 3,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,33</t>
+          <t>2,2; 3,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,65</t>
+          <t>0,87; 1,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,71</t>
+          <t>0,88; 1,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,92; 2,97</t>
+          <t>2,17; 3,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,9</t>
+          <t>3,0; 3,88</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,99</t>
+          <t>1,37; 2,03</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,91</t>
+          <t>1,33; 1,91</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 2,84</t>
+          <t>2,2; 2,92</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>8513</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5068; 17651</t>
+          <t>5142; 17436</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>959; 9592</t>
+          <t>949; 8838</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3199; 16538</t>
+          <t>2818; 15554</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1395; 8510</t>
+          <t>1554; 9421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4689</t>
+          <t>0; 5140</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1028; 12023</t>
+          <t>1043; 11994</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6212</t>
+          <t>0; 6311</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1932; 7593</t>
+          <t>1858; 7449</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5687; 18926</t>
+          <t>5288; 18884</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3198; 16121</t>
+          <t>3092; 15920</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3821; 18028</t>
+          <t>4085; 18364</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4615; 13465</t>
+          <t>4840; 14610</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9707</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>20896</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15720; 38205</t>
+          <t>15942; 36585</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9379; 27561</t>
+          <t>10199; 27788</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7314; 22235</t>
+          <t>7289; 21588</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5364; 18130</t>
+          <t>5398; 18431</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11761; 28545</t>
+          <t>11664; 28658</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2204; 12777</t>
+          <t>2162; 12146</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3313; 14270</t>
+          <t>3302; 15438</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5513; 17721</t>
+          <t>5792; 16665</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32205; 57160</t>
+          <t>31362; 58829</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13641; 34224</t>
+          <t>14404; 34076</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12940; 31526</t>
+          <t>13698; 32175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12773; 29501</t>
+          <t>13038; 31058</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21606</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7431; 22081</t>
+          <t>7232; 22901</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3334; 15121</t>
+          <t>3125; 15204</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1583; 9945</t>
+          <t>1475; 9440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5923; 17343</t>
+          <t>5954; 16255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>926; 8198</t>
+          <t>923; 8673</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1938; 11314</t>
+          <t>2048; 11592</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1040; 9144</t>
+          <t>1040; 9212</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7223; 16717</t>
+          <t>7245; 17381</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9460; 24839</t>
+          <t>9611; 25952</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6661; 21515</t>
+          <t>7105; 23201</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3518; 14793</t>
+          <t>3500; 14827</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14984; 28841</t>
+          <t>15165; 28839</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25808</t>
+          <t>28323</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9234; 23612</t>
+          <t>8924; 23932</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5408; 21844</t>
+          <t>5204; 20654</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4773; 16748</t>
+          <t>4795; 17303</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7346; 22011</t>
+          <t>7980; 24681</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2807; 13140</t>
+          <t>2251; 13113</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5001; 17950</t>
+          <t>4949; 18329</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1913; 11788</t>
+          <t>1991; 12373</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6990; 24887</t>
+          <t>8503; 27757</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13531; 31609</t>
+          <t>14104; 31984</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12508; 33238</t>
+          <t>12915; 31241</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8869; 23736</t>
+          <t>8649; 23400</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16855; 39818</t>
+          <t>18796; 43418</t>
         </is>
       </c>
     </row>
@@ -2988,29 +2988,29 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>3710</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8778</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>3499</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8778</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>970</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3369</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
           <t>17300</t>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>7209</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4060; 15676</t>
+          <t>3974; 15837</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1040; 10773</t>
+          <t>1011; 8760</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1644; 10459</t>
+          <t>1800; 10294</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1493; 7550</t>
+          <t>1559; 7996</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4113; 16209</t>
+          <t>3928; 17475</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4792</t>
+          <t>0; 6201</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6875</t>
+          <t>0; 6972</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1581; 6217</t>
+          <t>1593; 6491</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10748; 26937</t>
+          <t>10795; 26881</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1106; 10725</t>
+          <t>1093; 9695</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2863; 13326</t>
+          <t>2970; 12463</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4052; 11239</t>
+          <t>4332; 11941</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>21794</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1944; 11595</t>
+          <t>1978; 11753</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6370; 22273</t>
+          <t>6390; 22432</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>978; 8844</t>
+          <t>999; 9471</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8143; 18723</t>
+          <t>7621; 17566</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1028; 9254</t>
+          <t>1034; 8920</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>944; 7970</t>
+          <t>948; 8383</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1239; 10179</t>
+          <t>1168; 10351</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6073; 14460</t>
+          <t>6095; 14283</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4202; 15806</t>
+          <t>4127; 17058</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8333; 26006</t>
+          <t>8939; 25200</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3949; 15888</t>
+          <t>3934; 16105</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16277; 29830</t>
+          <t>16635; 30151</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17048</t>
+          <t>18579</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>24875</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>39018</t>
+          <t>43454</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>18275; 38049</t>
+          <t>18690; 38822</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3043; 14229</t>
+          <t>3025; 13439</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5690; 19829</t>
+          <t>5748; 20854</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10715; 26442</t>
+          <t>11323; 28399</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13055; 31200</t>
+          <t>13446; 32267</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3223; 14887</t>
+          <t>3284; 14223</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5095; 18592</t>
+          <t>5243; 19101</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10090; 35415</t>
+          <t>16462; 36053</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37740; 64690</t>
+          <t>36249; 63402</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8111; 23368</t>
+          <t>8502; 24543</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13596; 33648</t>
+          <t>13407; 33706</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21332; 52126</t>
+          <t>33265; 61771</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>29595</t>
+          <t>34018</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>21978; 44206</t>
+          <t>22889; 44304</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6491; 23020</t>
+          <t>5656; 22413</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6445; 20461</t>
+          <t>7249; 21334</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4876; 23339</t>
+          <t>9777; 23948</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>19287; 40272</t>
+          <t>19446; 42204</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2091; 12192</t>
+          <t>2081; 11968</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5648; 19963</t>
+          <t>5088; 19499</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10831; 22716</t>
+          <t>11739; 25890</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>47720; 80360</t>
+          <t>47632; 78162</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9836; 29448</t>
+          <t>10828; 28733</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14418; 33648</t>
+          <t>14808; 32913</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>18386; 42340</t>
+          <t>24928; 44634</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>83692</t>
+          <t>89995</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>95820</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>172262</t>
+          <t>185815</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>113437; 157978</t>
+          <t>116127; 161980</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>56944; 93437</t>
+          <t>55218; 91308</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51201; 83469</t>
+          <t>51915; 84355</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>62876; 101720</t>
+          <t>72487; 107672</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>73793; 112672</t>
+          <t>74356; 110814</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31756; 58506</t>
+          <t>30856; 57667</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33464; 60705</t>
+          <t>31237; 60482</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>70208; 108383</t>
+          <t>81023; 113973</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>198466; 259841</t>
+          <t>199435; 257911</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>95569; 139176</t>
+          <t>95606; 141689</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>91677; 132478</t>
+          <t>92622; 132714</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>144396; 201656</t>
+          <t>159961; 211854</t>
         </is>
       </c>
     </row>
